--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6802.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6802.xlsx
@@ -6246,9 +6246,27 @@
       <c r="D60" t="n">
         <v>0.5625</v>
       </c>
+      <c r="E60" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F60" t="n">
+        <v>60</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.2515</v>
+      </c>
       <c r="H60" t="n">
         <v>0.481</v>
       </c>
+      <c r="I60" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="K60" t="n">
+        <v>37</v>
+      </c>
       <c r="L60" t="n">
         <v>0.875</v>
       </c>
@@ -6282,12 +6300,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_THDL@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6802-06-10-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_THDL@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF, JIC_RELIEFL@DRIVE, RELIEFANG@DRIVE, JIC_THDZ@DRIVE, JIC_LANDL@DRIVE, JIC_SEATL@DRIVE, SEATB@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6802-06-10-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6802-06-10-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6802-06-10-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=A, LEG_JIC@DRIVE=M2, LEG_ORB@DRIVE=M8, ORB_GRVDIA@DRIVE=N, ORB_THDL@DRIVE=K, THDMAJ_A@DRIVE=THD1, THDMAJ_B@DRIVE=THD2, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6802-06-10-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6802-06-10-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=A, LEG_JIC@DRIVE=M2, LEG_ORB@DRIVE=M8, ORB_GRVDIA@DRIVE=N, ORB_THDL@DRIVE=K, THDMAJ_A@DRIVE=THD1, THDMAJ_B@DRIVE=THD2, Y@REF=Y, JIC_RELIEFL@DRIVE=ENDLIB, RELIEFANG@DRIVE=ENDLIB, JIC_THDZ@DRIVE=ENDLIB, JIC_LANDL@DRIVE=ENDLIB, JIC_SEATL@DRIVE=ENDLIB, SEATB@DRIVE=ENDLIB; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -6321,9 +6339,27 @@
       <c r="D61" t="n">
         <v>0.75</v>
       </c>
+      <c r="E61" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F61" t="n">
+        <v>60</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.2837</v>
+      </c>
       <c r="H61" t="n">
         <v>0.659</v>
       </c>
+      <c r="I61" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K61" t="n">
+        <v>37</v>
+      </c>
       <c r="L61" t="n">
         <v>1.0625</v>
       </c>
@@ -6357,12 +6393,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_THDL@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6802-08-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, HEXB@HEX, JIC_CONEDIA@DRIVE, LEG_JIC@DRIVE, LEG_ORB@DRIVE, ORB_GRVDIA@DRIVE, ORB_THDL@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE, Y@REF, JIC_RELIEFL@DRIVE, RELIEFANG@DRIVE, JIC_THDZ@DRIVE, JIC_LANDL@DRIVE, JIC_SEATL@DRIVE, SEATB@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6802-08-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6802-08-12-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6802-08-12-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=A, LEG_JIC@DRIVE=M2, LEG_ORB@DRIVE=M8, ORB_GRVDIA@DRIVE=N, ORB_THDL@DRIVE=K, THDMAJ_A@DRIVE=THD1, THDMAJ_B@DRIVE=THD2, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6802-08-12-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6802-08-12-NWO-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, HEXB@HEX=C, JIC_CONEDIA@DRIVE=A, LEG_JIC@DRIVE=M2, LEG_ORB@DRIVE=M8, ORB_GRVDIA@DRIVE=N, ORB_THDL@DRIVE=K, THDMAJ_A@DRIVE=THD1, THDMAJ_B@DRIVE=THD2, Y@REF=Y, JIC_RELIEFL@DRIVE=ENDLIB, RELIEFANG@DRIVE=ENDLIB, JIC_THDZ@DRIVE=ENDLIB, JIC_LANDL@DRIVE=ENDLIB, JIC_SEATL@DRIVE=ENDLIB, SEATB@DRIVE=ENDLIB; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
